--- a/Бюджет/Бюджет под чистовую — Берта Ромарио.xlsx
+++ b/Бюджет/Бюджет под чистовую — Берта Ромарио.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Под чистовую" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Свет Maytoni" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,15 +444,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -496,14 +495,14 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Строй Хауз: фундамент, стены, кровля (договор)</t>
+          <t>Строй Хауз: площадка, фундамент, брус, перекрытие, стропила, кровля, водосток (договор № 26/10-06/1)</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42000000</v>
+        <v>43500000</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>42000000</v>
+        <v>43500000</v>
       </c>
       <c r="E2" s="3">
         <f>(C2+D2)/2</f>
@@ -511,7 +510,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>фикс.</t>
+          <t>подписано 43,5; 42,0 после допсоглашения</t>
         </is>
       </c>
     </row>
@@ -523,20 +522,24 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Окна и витражи ≈ 229 м², энергосберегающие, с монтажом</t>
+          <t>Окна и витражи ≈ 224–230 м², Schüco / Alutech, с монтажом и опциями</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5725000</v>
+        <v>20900000</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>9160000</v>
+        <v>26500000</v>
       </c>
       <c r="E3" s="3">
         <f>(C3+D3)/2</f>
         <v/>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>тендер: КП до 31.10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -559,7 +562,11 @@
         <f>(C4+D4)/2</f>
         <v/>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>не входит в договор СХ</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -569,7 +576,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Фасад: шлифовка, покраска бруса, подшивка свесов, цоколь</t>
+          <t>Защитное покрытие бруса снаружи (в течение 30 дней после сборки — условие гарантии), цоколь</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
@@ -584,7 +591,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>если не входит в договор Строй Хауза</t>
+          <t>не входит в договор СХ</t>
         </is>
       </c>
     </row>
@@ -611,7 +618,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>если не входит в договор Строй Хауза</t>
+          <t>не входит в договор СХ</t>
         </is>
       </c>
     </row>
@@ -623,14 +630,14 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Стяжки пола по тёплому полу ≈ 438 м²</t>
+          <t>Стяжка с тёплым полом 1 этажа ≈ 210 м²</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>569000</v>
+        <v>273000</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>964000</v>
+        <v>462000</v>
       </c>
       <c r="E7" s="3">
         <f>(C7+D7)/2</f>
@@ -638,7 +645,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>если не входит в договор Строй Хауза</t>
+          <t>не входит в договор СХ</t>
         </is>
       </c>
     </row>
@@ -650,66 +657,78 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Лестница (каркас и ступени)</t>
+          <t>Лестница, схема Б: металлокаркас + бетон, отделка, ограждение</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>800000</v>
+        <v>850000</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2000000</v>
+        <v>1800000</v>
       </c>
       <c r="E8" s="3">
         <f>(C8+D8)/2</f>
         <v/>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>не входит в договор СХ</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Инженерия</t>
+          <t>Коробка</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Вентиляция и кондиционирование (ПВУ с рекуператором, VRF)</t>
+          <t>Камин дровяной с дымоходом и подводом воздуха</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>4840000</v>
+        <v>400000</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>8057000</v>
+        <v>1200000</v>
       </c>
       <c r="E9" s="3">
         <f>(C9+D9)/2</f>
         <v/>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>не входит в договор СХ</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Инженерия</t>
+          <t>Коробка</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Отопление: пеллетный котёл, котельная, тёплые полы, конвекторы</t>
+          <t>Отмостка</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>5731000</v>
+        <v>500000</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>10902000</v>
+        <v>900000</v>
       </c>
       <c r="E10" s="3">
         <f>(C10+D10)/2</f>
         <v/>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>не входит в договор СХ</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -719,14 +738,14 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Водопровод и канализация (без сантехприборов)</t>
+          <t>Вентиляция и кондиционирование, увлажнение</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>1028000</v>
+        <v>6674000</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2054000</v>
+        <v>11529000</v>
       </c>
       <c r="E11" s="3">
         <f>(C11+D11)/2</f>
@@ -742,14 +761,14 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Электрика: щиты, кабели, розетки, выключатели</t>
+          <t>Отопление и котельная (пеллеты + электро)</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>2121000</v>
+        <v>4164000</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4491000</v>
+        <v>8369000</v>
       </c>
       <c r="E12" s="3">
         <f>(C12+D12)/2</f>
@@ -765,24 +784,20 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Свет Maytoni во всём доме</t>
+          <t>Водопровод и канализация (без сантехприборов)</t>
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1550000</v>
+        <v>1185000</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4080000</v>
+        <v>2382000</v>
       </c>
       <c r="E13" s="3">
         <f>(C13+D13)/2</f>
         <v/>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>с монтажом и светопроектом</t>
-        </is>
-      </c>
+      <c r="F13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -792,14 +807,14 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Умный дом, сеть, Wi-Fi, видеонаблюдение, домофон</t>
+          <t>Электрика, свет Maytoni (−50 %), батарея и генератор</t>
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>858000</v>
+        <v>6081000</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>2144000</v>
+        <v>11784000</v>
       </c>
       <c r="E14" s="3">
         <f>(C14+D14)/2</f>
@@ -815,14 +830,14 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Молниезащита, заземление, пожарная сигнализация</t>
+          <t>Сеть, умный дом HA, камеры, домофон, охрана, базовое аудио</t>
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>515000</v>
+        <v>2042000</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1043000</v>
+        <v>4911000</v>
       </c>
       <c r="E15" s="3">
         <f>(C15+D15)/2</f>
@@ -838,41 +853,37 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Наружные сети и подключения (вода, канализация, 50 кВт, дренаж)</t>
+          <t>Аудио и кинозона сверх базового (5.1, экран/проектор)</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>980000</v>
+        <v>500000</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2468000</v>
+        <v>1500000</v>
       </c>
       <c r="E16" s="3">
         <f>(C16+D16)/2</f>
         <v/>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>до ТУ</t>
-        </is>
-      </c>
+      <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Организация</t>
+          <t>Инженерия</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Проекты, топосъёмка, технадзор</t>
+          <t>Приводы штор и карнизы 12–15 шт.</t>
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>690000</v>
+        <v>400000</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1590000</v>
+        <v>900000</v>
       </c>
       <c r="E17" s="3">
         <f>(C17+D17)/2</f>
@@ -883,19 +894,19 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Организация</t>
+          <t>Инженерия</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Временные сооружения, вывоз мусора, охрана</t>
+          <t>Программирование и пусконаладка умного дома (интегратор)</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
         <v>400000</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>800000</v>
+        <v>1000000</v>
       </c>
       <c r="E18" s="3">
         <f>(C18+D18)/2</f>
@@ -904,19 +915,21 @@
       <c r="F18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Инженерия</t>
+        </is>
+      </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Непредвиденные 7% (кроме договора Строй Хауз)</t>
-        </is>
-      </c>
-      <c r="C19" s="3">
-        <f>ROUND(0.07*SUM(C3:C18),-3)</f>
-        <v/>
-      </c>
-      <c r="D19" s="3">
-        <f>ROUND(0.07*SUM(D3:D18),-3)</f>
-        <v/>
+          <t>Молниезащита, заземление, пожарная сигнализация</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>617000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1220000</v>
       </c>
       <c r="E19" s="3">
         <f>(C19+D19)/2</f>
@@ -925,62 +938,96 @@
       <c r="F19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>ИТОГО под чистовую</t>
-        </is>
-      </c>
-      <c r="C20" s="5">
-        <f>SUM(C2:C19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="5">
-        <f>SUM(D2:D19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="5">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Инженерия</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Наружные сети и подключения (вода, канализация, кабель, дренаж)</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>880000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>2268000</v>
+      </c>
+      <c r="E20" s="3">
         <f>(C20+D20)/2</f>
         <v/>
       </c>
-      <c r="F20" s="4" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>до ТУ посёлка</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="n"/>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Организация</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Проектирование инженерии (тендер) и технадзор</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>750000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>1800000</v>
+      </c>
+      <c r="E21" s="3">
+        <f>(C21+D21)/2</f>
+        <v/>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Организация</t>
+        </is>
+      </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>После — не входит в итог</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>Стройплощадка вне договора: электроэнергия 15 кВт, вода, охрана, дизель</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>800000</v>
+      </c>
+      <c r="E22" s="3">
+        <f>(C22+D22)/2</f>
+        <v/>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>не входит в договор СХ</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Позже</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Чистовая отделка: полы, плитка, покраска, потолки, межкомнатные двери</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="n">
-        <v>8800000</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v>19500000</v>
+          <t>Непредвиденные 10–15 % (на незаконтрактованную часть)</t>
+        </is>
+      </c>
+      <c r="C23" s="3">
+        <f>ROUND(0.1*SUM(C3:C22),-3)</f>
+        <v/>
+      </c>
+      <c r="D23" s="3">
+        <f>ROUND(0.15*SUM(D3:D22),-3)</f>
+        <v/>
       </c>
       <c r="E23" s="3">
         <f>(C23+D23)/2</f>
@@ -989,72 +1036,44 @@
       <c r="F23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Позже</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Сантехприборы по дизайн-проекту</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>ИТОГО под чистовую</t>
+        </is>
+      </c>
+      <c r="C24" s="5">
+        <f>SUM(C2:C23)</f>
+        <v/>
+      </c>
+      <c r="D24" s="5">
+        <f>SUM(D2:D23)</f>
+        <v/>
+      </c>
+      <c r="E24" s="5">
         <f>(C24+D24)/2</f>
         <v/>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>Позже</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Газ, этап 2: котёл, газопровод по участку, проект</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="n">
-        <v>540000</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="E25" s="3">
-        <f>(C25+D25)/2</f>
-        <v/>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="n"/>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>Позже</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Благоустройство: отмостка, дорожки, озеленение</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="E26" s="3">
-        <f>(C26+D26)/2</f>
-        <v/>
-      </c>
+          <t>После — не входит в итог</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
       <c r="F26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1065,14 +1084,14 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>КНС — только если нет самотёка (по ТУ)</t>
+          <t>Чистовая отделка: полы, плитка, покраска бруса внутри, потолки, межкомнатные двери</t>
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>350000</v>
+        <v>8800000</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>800000</v>
+        <v>19500000</v>
       </c>
       <c r="E27" s="3">
         <f>(C27+D27)/2</f>
@@ -1080,403 +1099,74 @@
       </c>
       <c r="F27" s="2" t="inlineStr"/>
     </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Статья</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Кол-во</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Ед.</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Цена мин., ₽</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Цена макс., ₽</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Сумма мин., ₽</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Сумма макс., ₽</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Встраиваемые и накладные споты Maytoni Technical</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>75</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>3500</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F2" s="3">
-        <f>B2*D2</f>
-        <v/>
-      </c>
-      <c r="G2" s="3">
-        <f>B2*E2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Магнитный трек Maytoni (шинопровод с аксессуарами)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F3" s="3">
-        <f>B3*D3</f>
-        <v/>
-      </c>
-      <c r="G3" s="3">
-        <f>B3*E3</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Трековые светильники Maytoni</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>7000</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>16000</v>
-      </c>
-      <c r="F4" s="3">
-        <f>B4*D4</f>
-        <v/>
-      </c>
-      <c r="G4" s="3">
-        <f>B4*E4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Подвесные и настенные декоративные светильники Maytoni</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F5" s="3">
-        <f>B5*D5</f>
-        <v/>
-      </c>
-      <c r="G5" s="3">
-        <f>B5*E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Люстры второго света: холл и гостиная</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F6" s="3">
-        <f>B6*D6</f>
-        <v/>
-      </c>
-      <c r="G6" s="3">
-        <f>B6*E6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Светодиодный профиль: ниши, лестница, карнизы</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>м</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="F7" s="3">
-        <f>B7*D7</f>
-        <v/>
-      </c>
-      <c r="G7" s="3">
-        <f>B7*E7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Фасад и терраса, Maytoni Outdoor IP65</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F8" s="3">
-        <f>B8*D8</f>
-        <v/>
-      </c>
-      <c r="G8" s="3">
-        <f>B8*E8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Сауна и С/У: влагозащищённые IP44/IP54</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>10000</v>
-      </c>
-      <c r="F9" s="3">
-        <f>B9*D9</f>
-        <v/>
-      </c>
-      <c r="G9" s="3">
-        <f>B9*E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Блоки питания, диммеры DALI / 0–10 В</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>250000</v>
-      </c>
-      <c r="F10" s="3">
-        <f>B10*D10</f>
-        <v/>
-      </c>
-      <c r="G10" s="3">
-        <f>B10*E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Монтаж светильников, треков и профиля</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>190</v>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>точ.</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>800</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F11" s="3">
-        <f>B11*D11</f>
-        <v/>
-      </c>
-      <c r="G11" s="3">
-        <f>B11*E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Светотехнический проект (расчёт освещённости, раскладка)</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>компл.</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>200000</v>
-      </c>
-      <c r="F12" s="3">
-        <f>B12*D12</f>
-        <v/>
-      </c>
-      <c r="G12" s="3">
-        <f>B12*E12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>ИТОГО свет Maytoni</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="3">
-        <f>SUM(F2:F12)</f>
-        <v/>
-      </c>
-      <c r="G13" s="3">
-        <f>SUM(G2:G12)</f>
-        <v/>
-      </c>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Позже</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Сантехприборы по дизайн-проекту</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>3500000</v>
+      </c>
+      <c r="E28" s="3">
+        <f>(C28+D28)/2</f>
+        <v/>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Позже</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Газ, этап 2 (2028): котёл, газопровод по участку, проект</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>480000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1190000</v>
+      </c>
+      <c r="E29" s="3">
+        <f>(C29+D29)/2</f>
+        <v/>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Позже</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Благоустройство: дорожки, настилы, озеленение, забор и ворота</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="E30" s="3">
+        <f>(C30+D30)/2</f>
+        <v/>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
